--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/NEVADA_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/NEVADA_2012.xlsx
@@ -2490,7 +2490,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C119">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C170">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C199">
@@ -5971,7 +5971,7 @@
         <v>171</v>
       </c>
       <c r="D312">
-        <v>0.009519568000891</v>
+        <v>0.009519568000891002</v>
       </c>
     </row>
     <row r="313">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C719">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C795">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1140">
@@ -23244,7 +23244,7 @@
       </c>
       <c r="B1272" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1272">
